--- a/output/pdf_financials_xlsx/EATH.xlsx
+++ b/output/pdf_financials_xlsx/EATH.xlsx
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.392475</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.010064</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.007147</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000589</v>
       </c>
     </row>
     <row r="35">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.392475</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.010064</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.14</v>
+        <v>0.147147</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000589</v>
       </c>
     </row>
     <row r="37">
@@ -1347,16 +1347,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.392475</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.212237</v>
+        <v>0.202173</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.007147</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.000589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/EATH.xlsx
+++ b/output/pdf_financials_xlsx/EATH.xlsx
@@ -4716,7 +4716,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>0.34995</v>
       </c>
